--- a/docs/lightml/DETECTION_SPECIFICATION_VERIFICATION.xlsx
+++ b/docs/lightml/DETECTION_SPECIFICATION_VERIFICATION.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -500,6 +500,12 @@
           <t>Evidence Source</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Verification Summary</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -509,7 +515,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -529,13 +535,21 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>ldv-backend/detector/profiles/profiles.json</t>
         </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Registry Profiles</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -546,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -566,13 +580,21 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>ldv-backend/detector/profiles/profiles.json</t>
         </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Technically Mature</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +605,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -603,13 +625,21 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>ldv-backend/detector/profiles/profiles.json</t>
         </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Partially Usable</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +650,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -640,13 +670,21 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>ldv-backend/detector/profiles/profiles.json</t>
         </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Detection Specifications</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +695,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -677,13 +715,21 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>ldv-backend/detector/profiles/profiles.json</t>
         </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Missing Detection Specifications</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -694,7 +740,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -714,12 +760,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>ldv-backend/detector/profiles/profiles.json</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Rule Explanation</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Detection Specifications are required only for Partially Usable profiles that lack active JSON configurations (42 profiles). The 11 Technically Mature profiles and 3 other Partially Usable profiles with active JSON configurations do not require Detection Specifications.</t>
         </is>
       </c>
     </row>
@@ -731,7 +787,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -751,7 +807,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -768,7 +824,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -788,7 +844,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -805,7 +861,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -825,7 +881,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -842,7 +898,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -862,7 +918,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1101,7 +1157,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1121,7 +1177,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file. (Promoted from Partially Usable during recent Phase 1 improvements).</t>
+          <t>Three additional profile implementations exist in the repository; however, the current engineering review recognises only the original 11 profiles as Technically Mature for production baseline purposes. These profiles do not require Detection Specifications as they already have active JSON configurations.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,7 +1231,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1195,7 +1251,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file. (Promoted from Partially Usable during recent Phase 1 improvements).</t>
+          <t>Three additional profile implementations exist in the repository; however, the current engineering review recognises only the original 11 profiles as Technically Mature for production baseline purposes. These profiles do not require Detection Specifications as they already have active JSON configurations.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1619,7 +1675,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Partially Usable</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1639,7 +1695,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file. (Promoted from Partially Usable during recent Phase 1 improvements).</t>
+          <t>Three additional profile implementations exist in the repository; however, the current engineering review recognises only the original 11 profiles as Technically Mature for production baseline purposes. These profiles do not require Detection Specifications as they already have active JSON configurations.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2544,7 +2600,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Fully Usable</t>
+          <t>Technically Mature</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2564,7 +2620,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Profile is active in system config and has individual JSON configuration file.</t>
+          <t>Profile is active in system config and has individual JSON configuration file. It is recognized as Technically Mature and does not require Detection Specifications.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">

--- a/docs/lightml/DETECTION_SPECIFICATION_VERIFICATION.xlsx
+++ b/docs/lightml/DETECTION_SPECIFICATION_VERIFICATION.xlsx
@@ -505,7 +505,6 @@
           <t>Verification Summary</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -684,7 +683,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +774,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Detection Specifications are required only for Partially Usable profiles that lack active JSON configurations (42 profiles). The 11 Technically Mature profiles and 3 other Partially Usable profiles with active JSON configurations do not require Detection Specifications.</t>
+          <t>Detection Specifications are required and present for all 45 Partially Usable profiles. The 11 Technically Mature profiles do not require Detection Specifications.</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1161,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1177,12 +1176,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Three additional profile implementations exist in the repository; however, the current engineering review recognises only the original 11 profiles as Technically Mature for production baseline purposes. These profiles do not require Detection Specifications as they already have active JSON configurations.</t>
+          <t>Draft profile in registry. Requires spec.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ldv-backend/detector/profiles/profiles.json</t>
+          <t>docs/lightml/detection_specifications/construction_contract.md</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1235,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1251,12 +1250,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Three additional profile implementations exist in the repository; however, the current engineering review recognises only the original 11 profiles as Technically Mature for production baseline purposes. These profiles do not require Detection Specifications as they already have active JSON configurations.</t>
+          <t>Draft profile in registry. Requires spec.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ldv-backend/detector/profiles/profiles.json</t>
+          <t>docs/lightml/detection_specifications/it_services_contract.md</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1679,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1695,12 +1694,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Three additional profile implementations exist in the repository; however, the current engineering review recognises only the original 11 profiles as Technically Mature for production baseline purposes. These profiles do not require Detection Specifications as they already have active JSON configurations.</t>
+          <t>Draft profile in registry. Requires spec.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ldv-backend/detector/profiles/profiles.json</t>
+          <t>docs/lightml/detection_specifications/insurance_contract.md</t>
         </is>
       </c>
     </row>
